--- a/files/me-ADPER8902064464.xlsx
+++ b/files/me-ADPER8902064464.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3463-3463</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -688,18 +688,16 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hayoung Kim, 라 나, Dong-Hyuk Joo, Euigeon So, Seung-Hwan Yoo, Seung-Jong Bae, Soo-Jin Kim, Yeong-cheol Kwak, ByeongWoo Choi, K. Park, DalJu Park, YunPyo Lee, MyungWon Lee, YongDuk Shin</t>
+          <t>Hayoung Kim, 나라, Dong-Hyuk Joo, Euigeon So, Seung-Hwan Yoo, Seung-Jong Bae, Soo-Jin Kim, Yeong-cheol Kwak, ByeongWoo Choi, K. Park, DalJu Park, YunPyo Lee, MyungWon Lee, YongDuk Shin</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Journal of Climate Change Research</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>한국기후변화학회지</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -718,7 +716,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -773,7 +771,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -826,7 +824,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -879,7 +877,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -887,7 +885,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
@@ -904,18 +904,16 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Dong-Hyuk Joo, 라 나, Ha-Young Kim, Jaepil Cho, JuHyoung Lee, Suk-ho Song, DalJu Park, , YunPyo Lee, MyoungWon Lee, Seung-Hwan Yoo</t>
+          <t>Dong-Hyuk Joo, 나라, Ha-Young Kim, Jaepil Cho, JuHyoung Lee, Suk-ho Song, DalJu Park, , YunPyo Lee, MyoungWon Lee, Seung-Hwan Yoo</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Journal of Climate Change Research</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>한국기후변화학회지</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -934,7 +932,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>국내 기타</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -989,7 +987,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1042,7 +1040,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1095,7 +1093,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1148,7 +1146,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1156,7 +1154,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1209,7 +1209,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1254,7 +1256,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1262,7 +1264,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1307,7 +1311,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1360,7 +1364,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1415,7 +1419,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1468,7 +1472,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
